--- a/data/trans_orig/IP19C06-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/IP19C06-Provincia-trans_orig.xlsx
@@ -1459,7 +1459,7 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>2653</t>
+          <t>2663</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1474,7 +1474,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>7,51%</t>
+          <t>7,54%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1494,7 +1494,7 @@
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>2631</t>
+          <t>3015</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1509,7 +1509,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>3,78%</t>
+          <t>4,33%</t>
         </is>
       </c>
     </row>
@@ -1567,7 +1567,7 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>32676</t>
+          <t>32666</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
@@ -1582,7 +1582,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>92,49%</t>
+          <t>92,46%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1602,7 +1602,7 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>66990</t>
+          <t>66606</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
@@ -1617,7 +1617,7 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>96,22%</t>
+          <t>95,67%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -3174,7 +3174,7 @@
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>3916</t>
+          <t>3140</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3189,7 +3189,7 @@
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>5,26%</t>
+          <t>4,22%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3209,7 +3209,7 @@
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>3283</t>
+          <t>3429</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3224,7 +3224,7 @@
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>2,11%</t>
+          <t>2,2%</t>
         </is>
       </c>
     </row>
@@ -3282,7 +3282,7 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>70497</t>
+          <t>71273</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
@@ -3297,7 +3297,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>94,74%</t>
+          <t>95,78%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3317,7 +3317,7 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>152451</t>
+          <t>152305</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
@@ -3332,7 +3332,7 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>97,89%</t>
+          <t>97,8%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
@@ -3517,7 +3517,7 @@
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>3836</t>
+          <t>4001</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3532,7 +3532,7 @@
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>1,06%</t>
+          <t>1,11%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3552,7 +3552,7 @@
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>5225</t>
+          <t>4522</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3567,7 +3567,7 @@
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>0,73%</t>
+          <t>0,63%</t>
         </is>
       </c>
     </row>
@@ -3625,7 +3625,7 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>357895</t>
+          <t>357730</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
@@ -3640,7 +3640,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>98,94%</t>
+          <t>98,89%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3660,7 +3660,7 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>707436</t>
+          <t>708139</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
@@ -3675,7 +3675,7 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>99,27%</t>
+          <t>99,37%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
@@ -4061,7 +4061,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>4100</t>
+          <t>4421</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4076,7 +4076,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>18,32%</t>
+          <t>19,76%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4096,7 +4096,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>3820</t>
+          <t>3759</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4111,7 +4111,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>12,88%</t>
+          <t>12,68%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4131,7 +4131,7 @@
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>5146</t>
+          <t>5032</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4146,7 +4146,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>9,89%</t>
+          <t>9,67%</t>
         </is>
       </c>
     </row>
@@ -4169,7 +4169,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>18275</t>
+          <t>17954</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -4184,7 +4184,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>81,68%</t>
+          <t>80,24%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -4204,7 +4204,7 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>25839</t>
+          <t>25900</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
@@ -4219,7 +4219,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>87,12%</t>
+          <t>87,32%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -4239,7 +4239,7 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>46888</t>
+          <t>47002</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
@@ -4254,7 +4254,7 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>90,11%</t>
+          <t>90,33%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -5090,7 +5090,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>2461</t>
+          <t>2187</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5105,7 +5105,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>5,89%</t>
+          <t>5,23%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5160,7 +5160,7 @@
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>2227</t>
+          <t>2163</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5175,7 +5175,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>2,68%</t>
+          <t>2,6%</t>
         </is>
       </c>
     </row>
@@ -5198,7 +5198,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>39337</t>
+          <t>39611</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -5213,7 +5213,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>94,11%</t>
+          <t>94,77%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -5268,7 +5268,7 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>80797</t>
+          <t>80861</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
@@ -5283,7 +5283,7 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>97,32%</t>
+          <t>97,4%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
@@ -5811,7 +5811,7 @@
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>3865</t>
+          <t>2990</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5826,7 +5826,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>11,65%</t>
+          <t>9,02%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5846,7 +5846,7 @@
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>3756</t>
+          <t>4127</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5861,7 +5861,7 @@
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>5,48%</t>
+          <t>6,02%</t>
         </is>
       </c>
     </row>
@@ -5919,7 +5919,7 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>29294</t>
+          <t>30169</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
@@ -5934,7 +5934,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>88,35%</t>
+          <t>90,98%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -5954,7 +5954,7 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>64829</t>
+          <t>64458</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
@@ -5969,7 +5969,7 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>94,52%</t>
+          <t>93,98%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
@@ -6119,7 +6119,7 @@
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>4245</t>
+          <t>4209</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -6134,7 +6134,7 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>6,64%</t>
+          <t>6,58%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -6154,7 +6154,7 @@
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>3436</t>
+          <t>3149</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -6169,7 +6169,7 @@
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>5,12%</t>
+          <t>4,69%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -6184,12 +6184,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>621</t>
+          <t>622</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>5502</t>
+          <t>5587</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -6204,7 +6204,7 @@
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>4,2%</t>
+          <t>4,26%</t>
         </is>
       </c>
     </row>
@@ -6227,7 +6227,7 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>59724</t>
+          <t>59760</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
@@ -6242,7 +6242,7 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>93,36%</t>
+          <t>93,42%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
@@ -6262,7 +6262,7 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>63728</t>
+          <t>64015</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
@@ -6277,7 +6277,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>94,88%</t>
+          <t>95,31%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -6297,12 +6297,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>125631</t>
+          <t>125546</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>130512</t>
+          <t>130511</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -6312,7 +6312,7 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>95,8%</t>
+          <t>95,74%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
@@ -6462,7 +6462,7 @@
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>2941</t>
+          <t>2562</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6477,7 +6477,7 @@
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>3,78%</t>
+          <t>3,29%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6532,7 +6532,7 @@
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>2919</t>
+          <t>2897</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6547,7 +6547,7 @@
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>1,97%</t>
+          <t>1,96%</t>
         </is>
       </c>
     </row>
@@ -6570,7 +6570,7 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>74906</t>
+          <t>75285</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
@@ -6585,7 +6585,7 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>96,22%</t>
+          <t>96,71%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
@@ -6640,7 +6640,7 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>145015</t>
+          <t>145037</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
@@ -6655,7 +6655,7 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>98,03%</t>
+          <t>98,04%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
@@ -6800,12 +6800,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>1127</t>
+          <t>1128</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>7336</t>
+          <t>7279</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -6820,7 +6820,7 @@
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>2,07%</t>
+          <t>2,06%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -6835,12 +6835,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>622</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>6120</t>
+          <t>6206</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -6850,12 +6850,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>0,01%</t>
+          <t>0,17%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>1,67%</t>
+          <t>1,7%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -6870,12 +6870,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>2505</t>
+          <t>2520</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>10386</t>
+          <t>10312</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -6890,7 +6890,7 @@
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>1,44%</t>
+          <t>1,43%</t>
         </is>
       </c>
     </row>
@@ -6913,12 +6913,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>346655</t>
+          <t>346712</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>352864</t>
+          <t>352863</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -6928,7 +6928,7 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>97,93%</t>
+          <t>97,94%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
@@ -6948,12 +6948,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>359882</t>
+          <t>359796</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>365984</t>
+          <t>365380</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -6963,12 +6963,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>98,33%</t>
+          <t>98,3%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>99,99%</t>
+          <t>99,83%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -6983,12 +6983,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>709607</t>
+          <t>709681</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>717488</t>
+          <t>717473</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -6998,7 +6998,7 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>98,56%</t>
+          <t>98,57%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
@@ -7762,7 +7762,7 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>3520</t>
+          <t>3468</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -7777,7 +7777,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>6,2%</t>
+          <t>6,11%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -7797,7 +7797,7 @@
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>4222</t>
+          <t>3916</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7812,7 +7812,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>3,83%</t>
+          <t>3,55%</t>
         </is>
       </c>
     </row>
@@ -7870,7 +7870,7 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>53213</t>
+          <t>53265</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
@@ -7885,7 +7885,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>93,8%</t>
+          <t>93,89%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -7905,7 +7905,7 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>106019</t>
+          <t>106325</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
@@ -7920,7 +7920,7 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>96,17%</t>
+          <t>96,45%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -8756,7 +8756,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>3755</t>
+          <t>3359</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -8771,7 +8771,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>24,96%</t>
+          <t>22,33%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -8826,7 +8826,7 @@
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>3886</t>
+          <t>4491</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8841,7 +8841,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>12,1%</t>
+          <t>13,99%</t>
         </is>
       </c>
     </row>
@@ -8864,7 +8864,7 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>11289</t>
+          <t>11685</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
@@ -8879,7 +8879,7 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>75,04%</t>
+          <t>77,67%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -8934,7 +8934,7 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>28225</t>
+          <t>27620</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
@@ -8949,7 +8949,7 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>87,9%</t>
+          <t>86,01%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
@@ -9785,7 +9785,7 @@
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>2951</t>
+          <t>3543</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -9800,7 +9800,7 @@
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>3,72%</t>
+          <t>4,47%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -9855,7 +9855,7 @@
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>3435</t>
+          <t>3132</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -9870,7 +9870,7 @@
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>2,18%</t>
+          <t>1,98%</t>
         </is>
       </c>
     </row>
@@ -9893,7 +9893,7 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>76301</t>
+          <t>75709</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
@@ -9908,7 +9908,7 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>96,28%</t>
+          <t>95,53%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
@@ -9963,7 +9963,7 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>154475</t>
+          <t>154778</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
@@ -9978,7 +9978,7 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>97,82%</t>
+          <t>98,02%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
@@ -10128,7 +10128,7 @@
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>4644</t>
+          <t>4974</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -10143,7 +10143,7 @@
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>1,28%</t>
+          <t>1,37%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -10163,7 +10163,7 @@
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>3520</t>
+          <t>3513</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -10178,7 +10178,7 @@
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>0,96%</t>
+          <t>0,95%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -10193,12 +10193,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>619</t>
+          <t>612</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>6144</t>
+          <t>5975</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -10213,7 +10213,7 @@
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>0,84%</t>
+          <t>0,82%</t>
         </is>
       </c>
     </row>
@@ -10236,7 +10236,7 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>357974</t>
+          <t>357644</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
@@ -10251,7 +10251,7 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>98,72%</t>
+          <t>98,63%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
@@ -10271,7 +10271,7 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>364488</t>
+          <t>364495</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
@@ -10286,7 +10286,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>99,04%</t>
+          <t>99,05%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -10306,12 +10306,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>724482</t>
+          <t>724651</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>730007</t>
+          <t>730014</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -10321,7 +10321,7 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>99,16%</t>
+          <t>99,18%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
@@ -11388,12 +11388,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>533</t>
+          <t>534</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>4776</t>
+          <t>4941</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -11403,12 +11403,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>1,67%</t>
+          <t>1,68%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>15,01%</t>
+          <t>15,53%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -11428,7 +11428,7 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>6300</t>
+          <t>5836</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -11443,7 +11443,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>15,73%</t>
+          <t>14,57%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -11458,12 +11458,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>711</t>
+          <t>684</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>8732</t>
+          <t>8255</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -11473,12 +11473,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,99%</t>
+          <t>0,95%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>12,15%</t>
+          <t>11,49%</t>
         </is>
       </c>
     </row>
@@ -11501,12 +11501,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>27047</t>
+          <t>26882</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>31290</t>
+          <t>31289</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -11516,12 +11516,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>84,99%</t>
+          <t>84,47%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>98,33%</t>
+          <t>98,32%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -11536,7 +11536,7 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>33752</t>
+          <t>34216</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
@@ -11551,7 +11551,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>84,27%</t>
+          <t>85,43%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -11571,12 +11571,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>63142</t>
+          <t>63619</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>71163</t>
+          <t>71190</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -11586,12 +11586,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>87,85%</t>
+          <t>88,51%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>99,01%</t>
+          <t>99,05%</t>
         </is>
       </c>
     </row>
@@ -11731,12 +11731,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>670</t>
+          <t>719</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>5945</t>
+          <t>6270</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -11746,12 +11746,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,56%</t>
+          <t>1,68%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>13,88%</t>
+          <t>14,63%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -11801,12 +11801,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>620</t>
+          <t>634</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>6085</t>
+          <t>6121</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -11816,12 +11816,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,61%</t>
+          <t>0,62%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>5,99%</t>
+          <t>6,03%</t>
         </is>
       </c>
     </row>
@@ -11844,12 +11844,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>36898</t>
+          <t>36573</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>42173</t>
+          <t>42124</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -11859,12 +11859,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>86,12%</t>
+          <t>85,37%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>98,44%</t>
+          <t>98,32%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -11914,12 +11914,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>95419</t>
+          <t>95383</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>100884</t>
+          <t>100870</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -11929,12 +11929,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>94,01%</t>
+          <t>93,97%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>99,39%</t>
+          <t>99,38%</t>
         </is>
       </c>
     </row>
@@ -12760,12 +12760,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>393</t>
+          <t>383</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>4338</t>
+          <t>4597</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -12775,12 +12775,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>0,51%</t>
+          <t>0,49%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>5,58%</t>
+          <t>5,91%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -12800,7 +12800,7 @@
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>4700</t>
+          <t>5096</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -12815,7 +12815,7 @@
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>4,32%</t>
+          <t>4,69%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -12830,12 +12830,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>722</t>
+          <t>805</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>7191</t>
+          <t>7101</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -12845,12 +12845,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>0,39%</t>
+          <t>0,43%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>3,86%</t>
+          <t>3,81%</t>
         </is>
       </c>
     </row>
@@ -12873,12 +12873,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>73418</t>
+          <t>73159</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>77363</t>
+          <t>77373</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -12888,12 +12888,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>94,42%</t>
+          <t>94,09%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>99,49%</t>
+          <t>99,51%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -12908,7 +12908,7 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>103988</t>
+          <t>103592</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
@@ -12923,7 +12923,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>95,68%</t>
+          <t>95,31%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -12943,12 +12943,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>179253</t>
+          <t>179343</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>185722</t>
+          <t>185639</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -12958,12 +12958,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>96,14%</t>
+          <t>96,19%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>99,61%</t>
+          <t>99,57%</t>
         </is>
       </c>
     </row>
@@ -13446,12 +13446,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>2657</t>
+          <t>2765</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>10494</t>
+          <t>11093</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -13461,12 +13461,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>0,68%</t>
+          <t>0,71%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>2,68%</t>
+          <t>2,83%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -13486,7 +13486,7 @@
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>8558</t>
+          <t>8563</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -13516,12 +13516,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>4279</t>
+          <t>4082</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>15396</t>
+          <t>15143</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -13531,12 +13531,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>0,49%</t>
+          <t>0,47%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>1,76%</t>
+          <t>1,73%</t>
         </is>
       </c>
     </row>
@@ -13559,12 +13559,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>381139</t>
+          <t>380540</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>388976</t>
+          <t>388868</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -13574,12 +13574,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>97,32%</t>
+          <t>97,17%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>99,32%</t>
+          <t>99,29%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -13594,7 +13594,7 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>475886</t>
+          <t>475881</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
@@ -13629,12 +13629,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>860680</t>
+          <t>860933</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>871797</t>
+          <t>871994</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -13644,12 +13644,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>98,24%</t>
+          <t>98,27%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>99,51%</t>
+          <t>99,53%</t>
         </is>
       </c>
     </row>
